--- a/sample_data/Meridian_Vendor_Input_MAVIRA_completed.xlsx
+++ b/sample_data/Meridian_Vendor_Input_MAVIRA_completed.xlsx
@@ -798,7 +798,7 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>High. Weighted score 0.55 falls in the MEDIUM band (&gt;= 0.35). Factor scores, highest contribution first: Operational dependency 0.75 x 0.30 — Operational Dependency = 'High'; Data sensitivity 0.75 x 0.25 — Privileged access to production systems / service credentials (matched 'privileged access' in Data Classification); Regulatory exposure 0.50 x 0.15 — Privileged change capability over regulated production systems (matched 'privileged access'); Payment-flow involvement 0.40 x 0.15 — Supports payment or batch processing indirectly (matched 'batch'); Customer / data volume 0.00 x 0.15 — Data volume 'Not applicable' gives no customer-record quantity. Escalated Medium -&gt; High by rule 'privileged_production_access': Privileged access to production systems that run core processing (credential compromise path). Methodology 1.0.0+2ded6eb8.</t>
+          <t>High. Weighted score 0.55 falls in the MEDIUM band (&gt;= 0.35). Factor scores, highest contribution first: Operational dependency 0.75 x 0.30 — Operational Dependency = 'High'; Data sensitivity 0.75 x 0.25 — Privileged access to production systems / service credentials (matched 'privileged access' in Data Classification); Regulatory exposure 0.50 x 0.15 — Privileged change capability over regulated production systems (matched 'privileged access'); Payment-flow involvement 0.40 x 0.15 — Supports payment or batch processing indirectly (matched 'batch'); Customer / data volume 0.00 x 0.15 — Data volume 'Not applicable' gives no customer-record quantity. Escalated Medium -&gt; High by rule 'privileged_production_access': Privileged access to production systems that run core processing (credential compromise path). Methodology 1.1.0+85b80c18.</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
@@ -815,10 +815,10 @@
         <is>
           <t>"For enterprises using Automic, this means leveraging technologies like generative AI (GenAI), machine learning (ML), and predictive analytics to enhance existing automation workflows." — https://www.automworx.com/what-is-ai-enablement-in-automic-workload-automation/ (retrieved 06-10-2026; official_product_page; CACHED)
 "On-prem, you connect Automic to whichever LLM provider you already use cloud-hosted or a local model." — https://www.automworx.com/automic-automation-v26-turning-orchestration-into-the-control-center-for-enterprise-ai/ (retrieved 06-10-2026; official_product_page; CACHED)
+"The AI Assistant explains, troubleshoots, and generates scripts on request, including converting a Python script to PowerShell on the spot." — https://www.automworx.com/automic-automation-v26-turning-orchestration-into-the-control-center-for-enterprise-ai/ (retrieved 06-10-2026; official_product_page; CACHED)
 "Natural-language workflow building is part of this too." — https://www.automworx.com/automic-automation-v26-turning-orchestration-into-the-control-center-for-enterprise-ai/ (retrieved 06-10-2026; official_product_page; CACHED)
-"The AI Assistant explains, troubleshoots, and generates scripts on request, including converting a Python script to PowerShell on the spot." — https://www.automworx.com/automic-automation-v26-turning-orchestration-into-the-control-center-for-enterprise-ai/ (retrieved 06-10-2026; official_product_page; CACHED)
-"The AI assistant in Automic instantly analyzes the logs from the failed execution, explains the reason for the failure in plain English, and suggests a code snippet to fix the issue." — https://www.automworx.com/what-is-ai-enablement-in-automic-workload-automation/ (retrieved 06-10-2026; official_product_page; CACHED)
 "AI enablement isn’t just about adding a new feature; it’s about creating a smarter, more proactive automation ecosystem." — https://www.automworx.com/what-is-ai-enablement-in-automic-workload-automation/ (retrieved 06-10-2026; official_product_page; CACHED)
+"Automate troubleshooting: When a job fails, the AI assistant can analyze logs and reports, identify the problem, and even suggest potential fixes, drastically reducing mean time to repair." — https://www.automworx.com/what-is-ai-enablement-in-automic-workload-automation/ (retrieved 06-10-2026; official_product_page; CACHED)
 Scope: 2 sources checked, 16 searches performed.</t>
         </is>
       </c>
@@ -844,18 +844,18 @@
       </c>
       <c r="U5" s="5" t="inlineStr">
         <is>
-          <t>1. [P1 · within 15 days] Request written disclosure of AI sub-processors and model providers used in the Implementation service, including hosting region. No provider is publicly named.
-2. [P2 · within 30 days] Issue a targeted AI-usage questionnaire: public material is inconclusive and absence of public evidence is not evidence of absence. Ask directly whether AI or ML processes Meridian data in the Implementation service.
-3. [P2 · within 30 days] Obtain model input/output retention terms (prompts, logs, embeddings) and deletion commitments for Meridian data.
-4. [P2 · within 30 days] Obtain a contractual commitment that Meridian data is not used to train, fine-tune or evaluate vendor or third-party models.
-5. [P2 · within 30 days] Confirm whether AI features of the third-party platform the vendor implements are enabled in Meridian's environment, which LLM is configured, and whether job logs, scripts or credentials can reach that model.
-6. [P3 · within 60 days] Raise AI clauses at the next contract review: training restrictions, sub-processor change notification, human-oversight thresholds, and rights to review AI-related attestations.
-7. [P4 · within 90 days] Monitor the vendor's public AI disclosures and re-run this assessment every 6 months or on any material announcement.</t>
+          <t>1. [P1 · within 15 days] Request written disclosure of AI sub-processors and model providers used in the Implementation service, including hosting region and data residency. No provider is publicly named. (NIST AI RMF GV-6.2; OCC 2023-17 §III.C; NIST SP 800-161r1)
+2. [P2 · within 30 days] Issue a targeted AI-usage questionnaire: public material is inconclusive and absence of public evidence is not evidence of absence. Ask directly whether AI or ML processes Meridian data in the Implementation service. (NIST AI RMF MAP-1.1; FFIEC IT Handbook — Third-Party Risk)
+3. [P2 · within 30 days] Obtain model input/output retention terms (prompts, logs, embeddings) and deletion commitments for Meridian data. Confirm compliance with Meridian's records-retention policy and applicable regulatory requirements. (NIST AI RMF MS-2.6; FFIEC Information Security Handbook §IV.C)
+4. [P2 · within 30 days] Obtain a contractual commitment that Meridian data is not used to train, fine-tune or evaluate vendor or third-party models. Absence of such a clause is a material gap under current interagency AI guidance. (NIST AI RMF GV-1.6; OCC 2026-46; Fed SR 23-4)
+5. [P2 · within 30 days] Confirm whether AI features of the third-party platform the vendor implements are enabled in Meridian's environment, which LLM is configured, and whether job logs, scripts or credentials can reach that model. (NIST SP 800-161r1; OCC 2023-17 §III.B)
+6. [P3 · within 60 days] Raise AI clauses at the next contract review: training restrictions, sub-processor change notification, human-oversight thresholds, incident notification (≤72 hrs), and rights to audit AI-related attestations. (OCC 2023-17 §IV; NIST AI RMF GV-1.6; NIST CSF 2.0 GV.SC-07)
+7. [P4 · within 90 days] Monitor the vendor's public AI disclosures and re-run this assessment every 6 months or on any material AI-related announcement, product change, or regulatory action. (NIST AI RMF MS-2.8; NIST CSF 2.0 ID.RA-10)</t>
         </is>
       </c>
       <c r="V5" s="5" t="inlineStr">
         <is>
-          <t>Team MAVIRA / 06-10-2026; pending analyst review</t>
+          <t>Team MAVIRA / 12-10-2026; reviewed by Team MAVIRA (approved, 12-10-2026)</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>Critical. Weighted score 0.98 falls in the CRITICAL band (&gt;= 0.75). Factor scores, highest contribution first: Operational dependency 1.00 x 0.30 — Operational Dependency = 'Critical'; Data sensitivity 1.00 x 0.25 — Full customer financial records (master data, balances, transactions) (matched 'customer master' in Data Classification); Regulatory exposure 1.00 x 0.15 — Holds the system of record for regulated customer accounts (matched 'core banking'); Customer / data volume 1.00 x 0.15 — 240,000,000 records from annual volume '240 million transactions' (log-scaled between 1,000 and 100,000,000); Payment-flow involvement 0.90 x 0.15 — Core account and transaction processing (matched 'core account processing'). Methodology 1.0.0+2ded6eb8.</t>
+          <t>Critical. Weighted score 0.98 falls in the CRITICAL band (&gt;= 0.75). Factor scores, highest contribution first: Operational dependency 1.00 x 0.30 — Operational Dependency = 'Critical'; Data sensitivity 1.00 x 0.25 — Full customer financial records (master data, balances, transactions) (matched 'customer master' in Data Classification); Regulatory exposure 1.00 x 0.15 — Holds the system of record for regulated customer accounts (matched 'core banking'); Customer / data volume 1.00 x 0.15 — 240,000,000 records from annual volume '240 million transactions' (log-scaled between 1,000 and 100,000,000); Payment-flow involvement 0.90 x 0.15 — Core account and transaction processing (matched 'core account processing'). Methodology 1.1.0+85b80c18.</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr">
@@ -952,30 +952,32 @@
       </c>
       <c r="S6" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="T6" s="5" t="inlineStr">
         <is>
-          <t>High. Score 68/100 with AI presence index 0.80 (AI usage: YES; signal types: INTERNAL_OPERATIONAL_USE, PARTNER_DEPENDENCY, PRODUCT_FEATURE). Main drivers: Data exposure 0.80 (Data sensitivity 1.00 from the inventory, scaled by AI presence.); Operational dependency 0.80 (Operational dependency 1.00 from the inventory.); Decision impact 0.72 (Highest-impact AI type detected: Fraud Detection (0.90).); Regulatory exposure 0.80 (Regulatory exposure 1.00 from the criticality factors.). Not publicly disclosed and scored as unknown: AI sub-processor risk, Data retention, Model training on Meridian data, Contractual coverage. AI use is confirmed at vendor level but no public source ties it to the contracted service; AI presence is discounted accordingly and the gap is carried to the questionnaire.</t>
+          <t>Critical. Score 68/100 with AI presence index 0.80 (AI usage: YES; signal types: INTERNAL_OPERATIONAL_USE, PARTNER_DEPENDENCY, PRODUCT_FEATURE). Main drivers: Data exposure 0.80 (Data sensitivity 1.00 from the inventory, scaled by AI presence.); Operational dependency 0.80 (Operational dependency 1.00 from the inventory.); Decision impact 0.72 (Highest-impact AI type detected: Fraud Detection (0.90).); Regulatory exposure 0.80 (Regulatory exposure 1.00 from the criticality factors.). Not publicly disclosed and scored as unknown: AI sub-processor risk, Data retention, Model training on Meridian data, Contractual coverage. Raised High -&gt; Critical by rule 'confirmed_ai_critical_high_data_sensitivity': Confirmed AI in a Critical-tier vendor with high data sensitivity (≥0.8) — data exfiltration via model boundary is a material threat at this sensitivity level (NIST AI RMF MS-2.5, FFIEC SR 11-7). AI use is confirmed at vendor level but no public source ties it to the contracted service; AI presence is discounted accordingly and the gap is carried to the questionnaire.</t>
         </is>
       </c>
       <c r="U6" s="5" t="inlineStr">
         <is>
-          <t>1. [P1 · within 15 days] Request written disclosure of AI sub-processors and model providers used in the DNA core banking platform service, including hosting region. Publicly named at enterprise level only: Microsoft (Azure OpenAI / Foundry / Copilot).
-2. [P1 · within 15 days] Confirm whether Meridian customer data is sent to external or third-party models; obtain a data-flow diagram for AI components touching Meridian data.
-3. [P1 · within 15 days] Require documented human-oversight thresholds and override controls for AI-driven decisions (Fraud Detection, Risk Scoring).
-4. [P2 · within 30 days] Obtain model input/output retention terms (prompts, logs, embeddings) and deletion commitments for Meridian data.
-5. [P2 · within 30 days] Obtain a contractual commitment that Meridian data is not used to train, fine-tune or evaluate vendor or third-party models.
-6. [P2 · within 30 days] The vendor's own public disclosure flags reliance on third-party model safeguards. Request evidence of the controls it applies over third-party AI model integration.
-7. [P2 · within 30 days] Register the vendor on the AI sub-processor inventory and escalate to the Third-Party Risk Committee if disclosures are not received by the due date.
-8. [P3 · within 60 days] Raise AI clauses at the next contract review: training restrictions, sub-processor change notification, human-oversight thresholds, and rights to review AI-related attestations.
-9. [P4 · within 90 days] Monitor the vendor's public AI disclosures and re-run this assessment every 3 months or on any material announcement.</t>
+          <t>1. [P1 · within 15 days] Request written disclosure of AI sub-processors and model providers used in the DNA core banking platform service, including hosting region and data residency. Publicly named at enterprise level only: Microsoft (Azure OpenAI / Foundry / Copilot). (NIST AI RMF GV-6.2; OCC 2023-17 §III.C; NIST SP 800-161r1)
+2. [P1 · within 15 days] Confirm whether Meridian customer data is sent to external or third-party models; obtain a data-flow diagram for AI components touching Meridian data. Evaluate whether transmission falls within permitted uses under Gramm-Leach-Bliley and OCC guidance on third-party arrangements. (NIST AI RMF MS-2.5; OCC 2023-17; GLBA §501)
+3. [P1 · within 15 days] Require documented human-oversight thresholds and override controls for AI-driven decisions (Fraud Detection, Risk Scoring). Ensure explainability standards meet ECOA / fair-lending requirements where applicable. (NIST AI RMF GV-6.2; FFIEC SR 11-7; CFPB Circular 2022-03)
+4. [P2 · within 30 days] Obtain model input/output retention terms (prompts, logs, embeddings) and deletion commitments for Meridian data. Confirm compliance with Meridian's records-retention policy and applicable regulatory requirements. (NIST AI RMF MS-2.6; FFIEC Information Security Handbook §IV.C)
+5. [P2 · within 30 days] Obtain a contractual commitment that Meridian data is not used to train, fine-tune or evaluate vendor or third-party models. Absence of such a clause is a material gap under current interagency AI guidance. (NIST AI RMF GV-1.6; OCC 2026-46; Fed SR 23-4)
+6. [P2 · within 30 days] The vendor's own public disclosure flags reliance on third-party model safeguards. Request evidence of the controls it applies over third-party AI model integration, including OWASP LLM Top-10 mitigations for prompt injection and supply-chain risk. (OWASP LLM 2026 LLM01, LLM09; NIST AI RMF MS-2.3)
+7. [P2 · within 30 days] Evaluate whether the vendor's AI usage constitutes a 'model' under SR 11-7 / OCC 2011-12 and requires Meridian to extend its Model Risk Management programme to cover this third-party model. Document the determination. (FFIEC SR 11-7; OCC 2011-12; OCC 2023-17)
+8. [P2 · within 30 days] Register the vendor on the AI sub-processor inventory and escalate to the Third-Party Risk Committee if disclosures are not received by the due date. Consider whether a board-level AI risk disclosure is required. (OCC 2026-46; Fed SR 23-4; NIST AI RMF GV-1.1)
+9. [P3 · within 60 days] Raise AI clauses at the next contract review: training restrictions, sub-processor change notification, human-oversight thresholds, incident notification (≤72 hrs), and rights to audit AI-related attestations. (OCC 2023-17 §IV; NIST AI RMF GV-1.6; NIST CSF 2.0 GV.SC-07)
+10. [P3 · within 60 days] Include this vendor in Meridian's AI supply-chain risk inventory. Verify that the vendor's sub-processors are themselves subject to equivalent AI governance and incident-notification obligations. (NIST CSF 2.0 GV.SC-07; NIST SP 800-161r1 C-SCRM)
+11. [P4 · within 90 days] Monitor the vendor's public AI disclosures and re-run this assessment every 3 months or on any material AI-related announcement, product change, or regulatory action. (NIST AI RMF MS-2.8; NIST CSF 2.0 ID.RA-10)</t>
         </is>
       </c>
       <c r="V6" s="5" t="inlineStr">
         <is>
-          <t>Team MAVIRA / 06-10-2026; pending analyst review</t>
+          <t>Team MAVIRA / 12-10-2026; reviewed by Team MAVIRA (approved, 12-10-2026)</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1039,7 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>High. Weighted score 0.71 falls in the HIGH band (&gt;= 0.55). Factor scores, highest contribution first: Data sensitivity 1.00 x 0.25 — Tax identifiers / government identifiers for customers (matched 'tax identifier' in Data Classification); Operational dependency 0.50 x 0.30 — Operational Dependency = 'Moderate'; Regulatory exposure 1.00 x 0.15 — Produces regulatory notices or tax reporting (e.g. IRS documents) (matched 'irs'); Customer / data volume 1.00 x 0.15 — Data classification covers the entire customer base; Payment-flow involvement 0.10 x 0.15 — No payment-flow role in category, process or service. Methodology 1.0.0+2ded6eb8.</t>
+          <t>High. Weighted score 0.71 falls in the HIGH band (&gt;= 0.55). Factor scores, highest contribution first: Data sensitivity 1.00 x 0.25 — Tax identifiers / government identifiers for customers (matched 'tax identifier' in Data Classification); Operational dependency 0.50 x 0.30 — Operational Dependency = 'Moderate'; Regulatory exposure 1.00 x 0.15 — Produces regulatory notices or tax reporting (e.g. IRS documents) (matched 'irs'); Customer / data volume 1.00 x 0.15 — Data classification covers the entire customer base; Payment-flow involvement 0.10 x 0.15 — No payment-flow role in category, process or service. Methodology 1.1.0+85b80c18.</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr">
@@ -1078,13 +1080,13 @@
       </c>
       <c r="U7" s="5" t="inlineStr">
         <is>
-          <t>1. [P2 · within 30 days] Issue a targeted AI-usage questionnaire: public material is inconclusive and absence of public evidence is not evidence of absence. Ask directly whether AI or ML processes Meridian data in the Produces and distributes printed account statements and IRS service.
-2. [P4 · within 90 days] Monitor the vendor's public AI disclosures and re-run this assessment every 6 months or on any material announcement.</t>
+          <t>1. [P2 · within 30 days] Issue a targeted AI-usage questionnaire: public material is inconclusive and absence of public evidence is not evidence of absence. Ask directly whether AI or ML processes Meridian data in the Produces and distributes printed account statements and IRS service. (NIST AI RMF MAP-1.1; FFIEC IT Handbook — Third-Party Risk)
+2. [P4 · within 90 days] Monitor the vendor's public AI disclosures and re-run this assessment every 6 months or on any material AI-related announcement, product change, or regulatory action. (NIST AI RMF MS-2.8; NIST CSF 2.0 ID.RA-10)</t>
         </is>
       </c>
       <c r="V7" s="5" t="inlineStr">
         <is>
-          <t>Team MAVIRA / 06-10-2026; pending analyst review</t>
+          <t>Team MAVIRA / 12-10-2026; reviewed by Team MAVIRA (approved, 12-10-2026)</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1148,7 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Medium. Weighted score 0.52 falls in the MEDIUM band (&gt;= 0.35). Factor scores, highest contribution first: Data sensitivity 0.70 x 0.25 — Client portfolio, revenue or compensation data (matched 'portfolio' in Data Classification); Operational dependency 0.50 x 0.30 — Operational Dependency = 'Moderate'; Regulatory exposure 0.60 x 0.15 — Supports advisor compensation / wealth compliance obligations (matched 'advisor compensation'); Payment-flow involvement 0.40 x 0.15 — Supports payment or batch processing indirectly (matched 'commission'); Customer / data volume 0.32 x 0.15 — 38,000 records from customer population named in data classification (log-scaled between 1,000 and 100,000,000). Methodology 1.0.0+2ded6eb8.</t>
+          <t>Medium. Weighted score 0.52 falls in the MEDIUM band (&gt;= 0.35). Factor scores, highest contribution first: Data sensitivity 0.70 x 0.25 — Client portfolio, revenue or compensation data (matched 'portfolio' in Data Classification); Operational dependency 0.50 x 0.30 — Operational Dependency = 'Moderate'; Regulatory exposure 0.60 x 0.15 — Supports advisor compensation / wealth compliance obligations (matched 'advisor compensation'); Payment-flow involvement 0.40 x 0.15 — Supports payment or batch processing indirectly (matched 'commission'); Customer / data volume 0.32 x 0.15 — 38,000 records from customer population named in data classification (log-scaled between 1,000 and 100,000,000). Methodology 1.1.0+85b80c18.</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
@@ -1187,13 +1189,13 @@
       </c>
       <c r="U8" s="5" t="inlineStr">
         <is>
-          <t>1. [P3 · within 60 days] Add AI-usage confirmation questions to the next periodic due-diligence review; public material does not establish whether AI processes Meridian data.
-2. [P4 · within 90 days] Monitor the vendor's public AI disclosures and re-run this assessment every 12 months or on any material announcement.</t>
+          <t>1. [P3 · within 60 days] Add AI-usage confirmation questions to the next periodic due-diligence review; public material does not establish whether AI processes Meridian data. (NIST AI RMF MAP-1.1; FFIEC Third-Party Risk Guidance)
+2. [P4 · within 90 days] Monitor the vendor's public AI disclosures and re-run this assessment every 12 months or on any material AI-related announcement, product change, or regulatory action. (NIST AI RMF MS-2.8; NIST CSF 2.0 ID.RA-10)</t>
         </is>
       </c>
       <c r="V8" s="5" t="inlineStr">
         <is>
-          <t>Team MAVIRA / 06-10-2026; pending analyst review</t>
+          <t>Team MAVIRA / 12-10-2026; reviewed by Team MAVIRA (approved, 12-10-2026)</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1257,7 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>Critical. Weighted score 0.81 falls in the CRITICAL band (&gt;= 0.75). Factor scores, highest contribution first: Operational dependency 0.75 x 0.30 — Operational Dependency = 'High'; Data sensitivity 0.80 x 0.25 — Payment instructions, counterparty and account identifiers (matched 'payment instruction' in Data Classification); Payment-flow involvement 1.00 x 0.15 — Directly operates or transmits payments (clearing, settlement, RTP/ACH) (matched 'real-time payment'); Regulatory exposure 0.90 x 0.15 — Operates within regulated payment-system rules (RTP / ACH / clearing) (matched 'rtp'); Customer / data volume 0.66 x 0.15 — 2,100,000 records from annual volume '2.1 million messages' (log-scaled between 1,000 and 100,000,000). Methodology 1.0.0+2ded6eb8.</t>
+          <t>Critical. Weighted score 0.81 falls in the CRITICAL band (&gt;= 0.75). Factor scores, highest contribution first: Operational dependency 0.75 x 0.30 — Operational Dependency = 'High'; Data sensitivity 0.80 x 0.25 — Payment instructions, counterparty and account identifiers (matched 'payment instruction' in Data Classification); Payment-flow involvement 1.00 x 0.15 — Directly operates or transmits payments (clearing, settlement, RTP/ACH) (matched 'real-time payment'); Regulatory exposure 0.90 x 0.15 — Operates within regulated payment-system rules (RTP / ACH / clearing) (matched 'rtp'); Customer / data volume 0.66 x 0.15 — 2,100,000 records from annual volume '2.1 million messages' (log-scaled between 1,000 and 100,000,000). Methodology 1.1.0+85b80c18.</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr">
@@ -1271,8 +1273,8 @@
       <c r="P9" s="5" t="inlineStr">
         <is>
           <t>"BNY has AI-based anomaly detection in its own Payment Validation solution, including machine learning and advanced analytics." — https://www.bny.com/corporate/global/en/insights/ai-and-payments-fraud-an-evolving-landscape.html (retrieved 06-10-2026; official_insights_article; CACHED)
+"We have over 125 AI-enabled solutions in production ⁠–⁠ from predictive analytics and automation to anomaly detection ⁠–⁠ designed to help clients transform their business while optimizing our own infrastructure." — https://www.bny.com/corporate/global/en/about-us/technology-innovation/artificial-intelligence.html (retrieved 06-10-2026; official_ai_documentation; CACHED)
 "Digital employees handle everything from payment instruction validation to code security enhancements." — https://openai.com/index/bny/ (retrieved 06-10-2026; official_partner_announcement; CACHED)
-"We have over 125 AI-enabled solutions in production ⁠–⁠ from predictive analytics and automation to anomaly detection ⁠–⁠ designed to help clients transform their business while optimizing our own infrastructure." — https://www.bny.com/corporate/global/en/about-us/technology-innovation/artificial-intelligence.html (retrieved 06-10-2026; official_ai_documentation; CACHED)
 "From its start, Eliza was designed not just as a tool, but as a system of work, pairing BNY’s governance rigor with leading models—including OpenAI frontier models—to help employees build safely and confidently." — https://openai.com/index/bny/ (retrieved 06-10-2026; official_partner_announcement; CACHED)
 "OpenAI, the company behind ChatGPT, has spotlighted BNY’s forward-thinking approach to deploying AI across the organization to increase efficiency and drive change." — https://www.bny.com/corporate/global/en/about-us/technology-innovation/artificial-intelligence.html (retrieved 06-10-2026; official_ai_documentation; CACHED)
 "We are the first major bank to deploy an AI Supercomputer (powered by NVIDIA) to accelerate processing capacity and to launch AI enabled capabilities." — https://www.bny.com/corporate/global/en/about-us/technology-innovation/artificial-intelligence.html (retrieved 06-10-2026; official_ai_documentation; CACHED)</t>
@@ -1290,29 +1292,31 @@
       </c>
       <c r="S9" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="T9" s="5" t="inlineStr">
         <is>
-          <t>High. Score 62/100 with AI presence index 0.80 (AI usage: YES; signal types: INTERNAL_OPERATIONAL_USE, PRODUCT_FEATURE). Main drivers: Decision impact 0.80 (Highest-impact AI type detected: Agentic AI (1.00).); Data exposure 0.64 (Data sensitivity 0.80 from the inventory, scaled by AI presence.); Regulatory exposure 0.72 (Regulatory exposure 0.90 from the criticality factors.); Operational dependency 0.60 (Operational dependency 0.75 from the inventory.). Not publicly disclosed and scored as unknown: AI sub-processor risk, Data retention, Model training on Meridian data, Contractual coverage. AI use is confirmed at vendor level but no public source ties it to the contracted service; AI presence is discounted accordingly and the gap is carried to the questionnaire.</t>
+          <t>Critical. Score 62/100 with AI presence index 0.80 (AI usage: YES; signal types: INTERNAL_OPERATIONAL_USE, PRODUCT_FEATURE). Main drivers: Decision impact 0.80 (Highest-impact AI type detected: Agentic AI (1.00).); Data exposure 0.64 (Data sensitivity 0.80 from the inventory, scaled by AI presence.); Regulatory exposure 0.72 (Regulatory exposure 0.90 from the criticality factors.); Operational dependency 0.60 (Operational dependency 0.75 from the inventory.). Not publicly disclosed and scored as unknown: AI sub-processor risk, Data retention, Model training on Meridian data, Contractual coverage. Raised High -&gt; Critical by rule 'confirmed_ai_critical_high_data_sensitivity': Confirmed AI in a Critical-tier vendor with high data sensitivity (≥0.8) — data exfiltration via model boundary is a material threat at this sensitivity level (NIST AI RMF MS-2.5, FFIEC SR 11-7). AI use is confirmed at vendor level but no public source ties it to the contracted service; AI presence is discounted accordingly and the gap is carried to the questionnaire.</t>
         </is>
       </c>
       <c r="U9" s="5" t="inlineStr">
         <is>
-          <t>1. [P1 · within 15 days] Request written disclosure of AI sub-processors and model providers used in the Real Time Payments (RTP) transmission services service, including hosting region. Publicly named at enterprise level only: NVIDIA, OpenAI.
-2. [P1 · within 15 days] Confirm whether Meridian customer data is sent to external or third-party models; obtain a data-flow diagram for AI components touching Meridian data.
-3. [P1 · within 15 days] Require documented human-oversight thresholds and override controls for AI-driven decisions (Fraud Detection, AI-assisted Automation, Agentic AI).
-4. [P2 · within 30 days] Obtain model input/output retention terms (prompts, logs, embeddings) and deletion commitments for Meridian data.
-5. [P2 · within 30 days] Obtain a contractual commitment that Meridian data is not used to train, fine-tune or evaluate vendor or third-party models.
-6. [P2 · within 30 days] Register the vendor on the AI sub-processor inventory and escalate to the Third-Party Risk Committee if disclosures are not received by the due date.
-7. [P3 · within 60 days] Raise AI clauses at the next contract review: training restrictions, sub-processor change notification, human-oversight thresholds, and rights to review AI-related attestations.
-8. [P4 · within 90 days] Monitor the vendor's public AI disclosures and re-run this assessment every 3 months or on any material announcement.</t>
+          <t>1. [P1 · within 15 days] Request written disclosure of AI sub-processors and model providers used in the Real Time Payments (RTP) transmission services service, including hosting region and data residency. Publicly named at enterprise level only: NVIDIA, OpenAI. (NIST AI RMF GV-6.2; OCC 2023-17 §III.C; NIST SP 800-161r1)
+2. [P1 · within 15 days] Confirm whether Meridian customer data is sent to external or third-party models; obtain a data-flow diagram for AI components touching Meridian data. Evaluate whether transmission falls within permitted uses under Gramm-Leach-Bliley and OCC guidance on third-party arrangements. (NIST AI RMF MS-2.5; OCC 2023-17; GLBA §501)
+3. [P1 · within 15 days] Require documented human-oversight thresholds and override controls for AI-driven decisions (Fraud Detection, AI-assisted Automation, Agentic AI). Ensure explainability standards meet ECOA / fair-lending requirements where applicable. (NIST AI RMF GV-6.2; FFIEC SR 11-7; CFPB Circular 2022-03)
+4. [P2 · within 30 days] Obtain model input/output retention terms (prompts, logs, embeddings) and deletion commitments for Meridian data. Confirm compliance with Meridian's records-retention policy and applicable regulatory requirements. (NIST AI RMF MS-2.6; FFIEC Information Security Handbook §IV.C)
+5. [P2 · within 30 days] Obtain a contractual commitment that Meridian data is not used to train, fine-tune or evaluate vendor or third-party models. Absence of such a clause is a material gap under current interagency AI guidance. (NIST AI RMF GV-1.6; OCC 2026-46; Fed SR 23-4)
+6. [P2 · within 30 days] Evaluate whether the vendor's AI usage constitutes a 'model' under SR 11-7 / OCC 2011-12 and requires Meridian to extend its Model Risk Management programme to cover this third-party model. Document the determination. (FFIEC SR 11-7; OCC 2011-12; OCC 2023-17)
+7. [P2 · within 30 days] Register the vendor on the AI sub-processor inventory and escalate to the Third-Party Risk Committee if disclosures are not received by the due date. Consider whether a board-level AI risk disclosure is required. (OCC 2026-46; Fed SR 23-4; NIST AI RMF GV-1.1)
+8. [P3 · within 60 days] Raise AI clauses at the next contract review: training restrictions, sub-processor change notification, human-oversight thresholds, incident notification (≤72 hrs), and rights to audit AI-related attestations. (OCC 2023-17 §IV; NIST AI RMF GV-1.6; NIST CSF 2.0 GV.SC-07)
+9. [P3 · within 60 days] Include this vendor in Meridian's AI supply-chain risk inventory. Verify that the vendor's sub-processors are themselves subject to equivalent AI governance and incident-notification obligations. (NIST CSF 2.0 GV.SC-07; NIST SP 800-161r1 C-SCRM)
+10. [P4 · within 90 days] Monitor the vendor's public AI disclosures and re-run this assessment every 3 months or on any material AI-related announcement, product change, or regulatory action. (NIST AI RMF MS-2.8; NIST CSF 2.0 ID.RA-10)</t>
         </is>
       </c>
       <c r="V9" s="5" t="inlineStr">
         <is>
-          <t>Team MAVIRA / 06-10-2026; pending analyst review</t>
+          <t>Team MAVIRA / 12-10-2026; reviewed by Team MAVIRA (approved, 12-10-2026)</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1378,7 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>Critical. Weighted score 0.86 falls in the CRITICAL band (&gt;= 0.75). Factor scores, highest contribution first: Operational dependency 1.00 x 0.30 — Operational Dependency = 'Critical'; Data sensitivity 0.60 x 0.25 — Payment messages in transit only (matched 'in transit' in Data Classification); Payment-flow involvement 1.00 x 0.15 — Directly operates or transmits payments (clearing, settlement, RTP/ACH) (matched 'clearing'); Regulatory exposure 0.90 x 0.15 — Operates within regulated payment-system rules (RTP / ACH / clearing) (matched 'rtp'); Customer / data volume 0.83 x 0.15 — 14,000,000 records from annual volume '14 million messages' (log-scaled between 1,000 and 100,000,000). Methodology 1.0.0+2ded6eb8.</t>
+          <t>Critical. Weighted score 0.86 falls in the CRITICAL band (&gt;= 0.75). Factor scores, highest contribution first: Operational dependency 1.00 x 0.30 — Operational Dependency = 'Critical'; Data sensitivity 0.60 x 0.25 — Payment messages in transit only (matched 'in transit' in Data Classification); Payment-flow involvement 1.00 x 0.15 — Directly operates or transmits payments (clearing, settlement, RTP/ACH) (matched 'clearing'); Regulatory exposure 0.90 x 0.15 — Operates within regulated payment-system rules (RTP / ACH / clearing) (matched 'rtp'); Customer / data volume 0.83 x 0.15 — 14,000,000 records from annual volume '14 million messages' (log-scaled between 1,000 and 100,000,000). Methodology 1.1.0+85b80c18.</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
@@ -1414,13 +1418,13 @@
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
-          <t>1. [P2 · within 30 days] Issue a targeted AI-usage questionnaire: public material is inconclusive and absence of public evidence is not evidence of absence. Ask directly whether AI or ML processes Meridian data in the Payment network infrastructure services service.
-2. [P4 · within 90 days] Monitor the vendor's public AI disclosures and re-run this assessment every 3 months or on any material announcement.</t>
+          <t>1. [P2 · within 30 days] Issue a targeted AI-usage questionnaire: public material is inconclusive and absence of public evidence is not evidence of absence. Ask directly whether AI or ML processes Meridian data in the Payment network infrastructure services service. (NIST AI RMF MAP-1.1; FFIEC IT Handbook — Third-Party Risk)
+2. [P4 · within 90 days] Monitor the vendor's public AI disclosures and re-run this assessment every 3 months or on any material AI-related announcement, product change, or regulatory action. (NIST AI RMF MS-2.8; NIST CSF 2.0 ID.RA-10)</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>Team MAVIRA / 06-10-2026; pending analyst review</t>
+          <t>Team MAVIRA / 12-10-2026; reviewed by Team MAVIRA (approved, 12-10-2026)</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2025,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>b08fade3ac63</t>
+          <t>2d9edd76b57b</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -2104,7 +2108,7 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>372a254fabab</t>
+          <t>a58791379390</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
@@ -2187,12 +2191,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>de3a71edb03b</t>
+          <t>32dcbe7e76b2</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Natural-language workflow building is part of this too.</t>
+          <t>The AI Assistant explains, troubleshoots, and generates scripts on request, including converting a Python script to PowerShell on the spot.</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -2232,7 +2236,7 @@
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>NLP, AI-assisted Automation</t>
+          <t>Generative AI, AI-assisted Automation</t>
         </is>
       </c>
       <c r="M4" s="7" t="n">
@@ -2270,12 +2274,12 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>ff96b4d025e2</t>
+          <t>ef0986b99638</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>The AI Assistant explains, troubleshoots, and generates scripts on request, including converting a Python script to PowerShell on the spot.</t>
+          <t>Natural-language workflow building is part of this too.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -2315,7 +2319,7 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>Generative AI, AI-assisted Automation</t>
+          <t>NLP, AI-assisted Automation</t>
         </is>
       </c>
       <c r="M5" s="7" t="n">
@@ -2353,12 +2357,12 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>3cf0e5264900</t>
+          <t>4f8655eebec4</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>The AI assistant in Automic instantly analyzes the logs from the failed execution, explains the reason for the failure in plain English, and suggests a code snippet to fix the issue.</t>
+          <t>AI enablement isn’t just about adding a new feature; it’s about creating a smarter, more proactive automation ecosystem.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -2398,7 +2402,7 @@
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>NLP</t>
+          <t>AI-assisted Automation</t>
         </is>
       </c>
       <c r="M6" s="7" t="n">
@@ -2414,7 +2418,7 @@
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>Classified PARTNER_DEPENDENCY: describes AI in third-party platform the vendor implements (Automic). Service relevance 0.25 (matched: automic); no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
+          <t>Classified PARTNER_DEPENDENCY: describes AI in third-party platform the vendor implements (Automic). Service relevance 0.25 (matched: automation); no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
@@ -2436,12 +2440,12 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>5072d5dd3d22</t>
+          <t>a660215daa71</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>AI enablement isn’t just about adding a new feature; it’s about creating a smarter, more proactive automation ecosystem.</t>
+          <t>Automate troubleshooting: When a job fails, the AI assistant can analyze logs and reports, identify the problem, and even suggest potential fixes, drastically reducing mean time to repair.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -2497,7 +2501,7 @@
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>Classified PARTNER_DEPENDENCY: describes AI in third-party platform the vendor implements (Automic). Service relevance 0.25 (matched: automation); no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
+          <t>Classified PARTNER_DEPENDENCY: describes AI in third-party platform the vendor implements (Automic). Service relevance 0.25 (matched: job); no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
@@ -2519,12 +2523,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>93c7cc43322d</t>
+          <t>105687dea6bb</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Automate troubleshooting: When a job fails, the AI assistant can analyze logs and reports, identify the problem, and even suggest potential fixes, drastically reducing mean time to repair.</t>
+          <t>The AI assistant in Automic instantly analyzes the logs from the failed execution, explains the reason for the failure in plain English, and suggests a code snippet to fix the issue.</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -2564,7 +2568,7 @@
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>AI-assisted Automation</t>
+          <t>NLP</t>
         </is>
       </c>
       <c r="M8" s="7" t="n">
@@ -2580,7 +2584,7 @@
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>Classified PARTNER_DEPENDENCY: describes AI in third-party platform the vendor implements (Automic). Service relevance 0.25 (matched: job); no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
+          <t>Classified PARTNER_DEPENDENCY: describes AI in third-party platform the vendor implements (Automic). Service relevance 0.25 (matched: automic); no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
         </is>
       </c>
       <c r="Q8" s="7" t="inlineStr">
@@ -2602,7 +2606,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>a210248399f6</t>
+          <t>77e835f2a8fb</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -2685,12 +2689,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>46b9df179ef4</t>
+          <t>d37e04626804</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>AI-assisted scripting and workflow building.</t>
+          <t>Bring your own LLM. On SaaS, a default model comes built in.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -2730,7 +2734,7 @@
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>AI-assisted Automation</t>
+          <t>Generative AI</t>
         </is>
       </c>
       <c r="M10" s="7" t="n">
@@ -2768,12 +2772,12 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>c74409636600</t>
+          <t>4a00642e892d</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Bring your own LLM. On SaaS, a default model comes built in.</t>
+          <t>AI-assisted scripting and workflow building.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -2813,7 +2817,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>Generative AI</t>
+          <t>AI-assisted Automation</t>
         </is>
       </c>
       <c r="M11" s="7" t="n">
@@ -2841,37 +2845,37 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>V-003</t>
+          <t>V-002</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Financial Statement Services, Inc. (FSSI)</t>
+          <t>Fiserv, Inc.</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>5a42431a78f5</t>
+          <t>58a570c27bf2</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>By leveraging artificial intelligence and machine learning, we can tap into the vast amount of customer data available to us.</t>
+          <t>To date, Fiserv has processed more than 100 billion tokens in Foundry, enhancing products, client servicing experiences, and its proprietary developer gateway.</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>https://www.fssi-ca.com/use-predictive-analytics-to-forecast-your-consumers-next-purchase/</t>
+          <t>https://investors.fiserv.com/news-releases/news-release-details/fiserv-collaborates-microsoft-accelerate-ai-driven-innovation</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>official_product_page</t>
+          <t>official_press_release</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -2886,33 +2890,33 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>2017-03-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>MARKETING_ONLY</t>
+          <t>PRODUCT_FEATURE</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Generative AI</t>
         </is>
       </c>
       <c r="M12" s="7" t="n">
-        <v>62.5</v>
+        <v>76.5</v>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>MODERATE</t>
+          <t>STRONG</t>
         </is>
       </c>
       <c r="O12" s="7" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>Classified MARKETING_ONLY: capability or aspirational language 'can' without a concrete deployment statement. Service relevance 0.00; no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
+          <t>Classified PRODUCT_FEATURE: concrete deployment language 'processed' tied to products/clients. Service relevance 0.50 (matched: client servic, servicing); no service-specific term — treated as vendor-level, not confirmed in the contracted service. Named provider(s): Microsoft (Azure OpenAI / Foundry / Copilot).</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
@@ -2924,37 +2928,37 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>V-003</t>
+          <t>V-002</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Financial Statement Services, Inc. (FSSI)</t>
+          <t>Fiserv, Inc.</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>0a582230d531</t>
+          <t>21ec12e65dc1</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>AI has grown smarter with each passing day, thanks to machine learning capabilities.</t>
+          <t>Across Fiserv, AI already powers fraud detection, risk management, and personalized engagement for financial institutions; enables smarter decisioning and higher authorization rates for merchants; and improves client servicing, compliance, and developer productivity.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>https://www.fssi-ca.com/use-predictive-analytics-to-forecast-your-consumers-next-purchase/</t>
+          <t>https://investors.fiserv.com/news-releases/news-release-details/fiserv-collaborates-microsoft-accelerate-ai-driven-innovation</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>official_product_page</t>
+          <t>official_press_release</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -2969,25 +2973,25 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>2017-03-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>INDUSTRY_COMMENTARY</t>
+          <t>PRODUCT_FEATURE</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Fraud Detection, Risk Scoring, Recommendation Systems</t>
         </is>
       </c>
       <c r="M13" s="7" t="n">
-        <v>46.5</v>
+        <v>75</v>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>MODERATE</t>
+          <t>STRONG</t>
         </is>
       </c>
       <c r="O13" s="7" t="n">
@@ -2995,7 +2999,7 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>Classified INDUSTRY_COMMENTARY: commentary/advocacy cue 'grown smarter'. Service relevance 0.00; no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
+          <t>Classified PRODUCT_FEATURE: concrete deployment language 'already' tied to products/clients. Service relevance 0.60 (matched: client servic, financial institutions, servicing); no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
@@ -3007,37 +3011,37 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>V-003</t>
+          <t>V-002</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Financial Statement Services, Inc. (FSSI)</t>
+          <t>Fiserv, Inc.</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>b2999035db13</t>
+          <t>ba79500473c2</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>And the future of predictive analytics lies in the realm of artificial intelligence (AI).</t>
+          <t>Fiserv will deploy Microsoft 365 Copilot across its global workforce, equipping employees with access to advanced AI tools that enhance productivity, accelerate decision-making, and elevate the quality of work.</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>https://www.fssi-ca.com/use-predictive-analytics-to-forecast-your-consumers-next-purchase/</t>
+          <t>https://investors.fiserv.com/news-releases/news-release-details/fiserv-collaborates-microsoft-accelerate-ai-driven-innovation</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>official_product_page</t>
+          <t>official_press_release</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -3052,33 +3056,33 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>2017-03-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>INDUSTRY_COMMENTARY</t>
+          <t>INTERNAL_OPERATIONAL_USE</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>Predictive Analytics</t>
+          <t>Generative AI</t>
         </is>
       </c>
       <c r="M14" s="7" t="n">
-        <v>46.5</v>
+        <v>69</v>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>MODERATE</t>
+          <t>STRONG</t>
         </is>
       </c>
       <c r="O14" s="7" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>Classified INDUSTRY_COMMENTARY: commentary/advocacy cue 'future of'. Service relevance 0.00; no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
+          <t>Classified INTERNAL_OPERATIONAL_USE: workforce/internal cue 'workforce'. Service relevance 0.00; no service-specific term — treated as vendor-level, not confirmed in the contracted service. Named provider(s): Microsoft (Azure OpenAI / Foundry / Copilot).</t>
         </is>
       </c>
       <c r="Q14" s="7" t="inlineStr">
@@ -3100,12 +3104,12 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>a754d574fc66</t>
+          <t>af969d09d182</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>To date, Fiserv has processed more than 100 billion tokens in Foundry, enhancing products, client servicing experiences, and its proprietary developer gateway.</t>
+          <t>This expanded relationship with Microsoft builds on Fiserv’s existing use of Microsoft Foundry and deployment of Microsoft’s GitHub Copilot.</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -3140,7 +3144,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>PRODUCT_FEATURE</t>
+          <t>INTERNAL_OPERATIONAL_USE</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -3149,7 +3153,7 @@
         </is>
       </c>
       <c r="M15" s="7" t="n">
-        <v>76.5</v>
+        <v>67</v>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
@@ -3157,11 +3161,11 @@
         </is>
       </c>
       <c r="O15" s="7" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>Classified PRODUCT_FEATURE: concrete deployment language 'processed' tied to products/clients. Service relevance 0.50 (matched: client servic, servicing); no service-specific term — treated as vendor-level, not confirmed in the contracted service. Named provider(s): Microsoft (Azure OpenAI / Foundry / Copilot).</t>
+          <t>Classified INTERNAL_OPERATIONAL_USE: concrete use without client/product reference. Service relevance 0.00; no service-specific term — treated as vendor-level, not confirmed in the contracted service. Named provider(s): Microsoft (Azure OpenAI / Foundry / Copilot).</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
@@ -3183,12 +3187,12 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>834fb69a99b8</t>
+          <t>020aba9e22fa</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Across Fiserv, AI already powers fraud detection, risk management, and personalized engagement for financial institutions; enables smarter decisioning and higher authorization rates for merchants; and improves client servicing, compliance, and developer productivity.</t>
+          <t>In parallel, Fiserv is working with Microsoft to expand its use of Microsoft Foundry, an Azure-powered AI platform designed to build, customize, deploy, and manage AI applications safely and securely.</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -3223,28 +3227,28 @@
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>PRODUCT_FEATURE</t>
+          <t>INTERNAL_OPERATIONAL_USE</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>Fraud Detection, Risk Scoring, Recommendation Systems</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="M16" s="7" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>STRONG</t>
+          <t>MODERATE</t>
         </is>
       </c>
       <c r="O16" s="7" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>Classified PRODUCT_FEATURE: concrete deployment language 'already' tied to products/clients. Service relevance 0.60 (matched: client servic, financial institutions, servicing); no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
+          <t>Classified INTERNAL_OPERATIONAL_USE: concrete use without client/product reference. Service relevance 0.00; no service-specific term — treated as vendor-level, not confirmed in the contracted service. Named provider(s): Microsoft (Azure OpenAI / Foundry / Copilot).</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
@@ -3266,12 +3270,12 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>2fee4e839613</t>
+          <t>b3c63016af58</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Fiserv will deploy Microsoft 365 Copilot across its global workforce, equipping employees with access to advanced AI tools that enhance productivity, accelerate decision-making, and elevate the quality of work.</t>
+          <t>The factors that could cause Fiserv’s actual results to differ materially include, among others: Fiserv and Microsoft’s ability to successfully deploy and embed artificial intelligence solutions into its platforms and operations; exposure to liability as a result of any misuse of artificial intelligence by Fiserv’s personnel; the integration of third-party artificial intelligence models with our services relies on certain safeguards implemented by the third-party developers which may be insufficient; and other factors included in “Risks Factors” in Fiserv’s filings with the SEC.</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -3306,28 +3310,28 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>INTERNAL_OPERATIONAL_USE</t>
+          <t>PARTNER_DEPENDENCY</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>Generative AI</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="M17" s="7" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>STRONG</t>
+          <t>MODERATE</t>
         </is>
       </c>
       <c r="O17" s="7" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>Classified INTERNAL_OPERATIONAL_USE: workforce/internal cue 'workforce'. Service relevance 0.00; no service-specific term — treated as vendor-level, not confirmed in the contracted service. Named provider(s): Microsoft (Azure OpenAI / Foundry / Copilot).</t>
+          <t>Classified PARTNER_DEPENDENCY: vendor's own statement that its services integrate third-party AI models. Service relevance 0.00; no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
@@ -3349,22 +3353,22 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>9beec09afa17</t>
+          <t>6889afc04016</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>This expanded relationship with Microsoft builds on Fiserv’s existing use of Microsoft Foundry and deployment of Microsoft’s GitHub Copilot.</t>
+          <t>The team at Fiserv has seen an increasing number of AI use cases around client services and support, fraud prevention and even loan origination.</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>https://investors.fiserv.com/news-releases/news-release-details/fiserv-collaborates-microsoft-accelerate-ai-driven-innovation</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-4-technologies-shaping-the-future-of-financial-services.html</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>official_press_release</t>
+          <t>official_insights_article</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
@@ -3384,21 +3388,21 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>INTERNAL_OPERATIONAL_USE</t>
+          <t>INDUSTRY_COMMENTARY</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>Generative AI</t>
+          <t>Fraud Detection</t>
         </is>
       </c>
       <c r="M18" s="7" t="n">
-        <v>67</v>
+        <v>70.5</v>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
@@ -3406,11 +3410,11 @@
         </is>
       </c>
       <c r="O18" s="7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>Classified INTERNAL_OPERATIONAL_USE: concrete use without client/product reference. Service relevance 0.00; no service-specific term — treated as vendor-level, not confirmed in the contracted service. Named provider(s): Microsoft (Azure OpenAI / Foundry / Copilot).</t>
+          <t>Classified INDUSTRY_COMMENTARY: commentary/advocacy cue 'has seen'. Service relevance 0.50 (matched: client servic, loan); no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
@@ -3432,22 +3436,22 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>b82c9515c042</t>
+          <t>d0767faf0cb5</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>In parallel, Fiserv is working with Microsoft to expand its use of Microsoft Foundry, an Azure-powered AI platform designed to build, customize, deploy, and manage AI applications safely and securely.</t>
+          <t>And White predicts the impact of AI on financial services will grow even larger as the industry addresses issues such as unintentional bias and privacy risk.</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>https://investors.fiserv.com/news-releases/news-release-details/fiserv-collaborates-microsoft-accelerate-ai-driven-innovation</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-4-technologies-shaping-the-future-of-financial-services.html</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>official_press_release</t>
+          <t>official_insights_article</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -3467,12 +3471,12 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>INTERNAL_OPERATIONAL_USE</t>
+          <t>INDUSTRY_COMMENTARY</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -3481,7 +3485,7 @@
         </is>
       </c>
       <c r="M19" s="7" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
@@ -3489,11 +3493,11 @@
         </is>
       </c>
       <c r="O19" s="7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>Classified INTERNAL_OPERATIONAL_USE: concrete use without client/product reference. Service relevance 0.00; no service-specific term — treated as vendor-level, not confirmed in the contracted service. Named provider(s): Microsoft (Azure OpenAI / Foundry / Copilot).</t>
+          <t>Classified INDUSTRY_COMMENTARY: commentary/advocacy cue 'predicts'. Service relevance 0.00; no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
@@ -3515,22 +3519,22 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>55a1d4e2f82e</t>
+          <t>42831e65621e</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>The factors that could cause Fiserv’s actual results to differ materially include, among others: Fiserv and Microsoft’s ability to successfully deploy and embed artificial intelligence solutions into its platforms and operations; exposure to liability as a result of any misuse of artificial intelligence by Fiserv’s personnel; the integration of third-party artificial intelligence models with our services relies on certain safeguards implemented by the third-party developers which may be insufficient; and other factors included in “Risks Factors” in Fiserv’s filings with the SEC.</t>
+          <t>Although AI is likely the murkiest advancement reshaping core banking modernization, White believes “the writing is on the wall that this is where the industry is moving.”</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>https://investors.fiserv.com/news-releases/news-release-details/fiserv-collaborates-microsoft-accelerate-ai-driven-innovation</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-4-technologies-shaping-the-future-of-financial-services.html</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>official_press_release</t>
+          <t>official_insights_article</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
@@ -3550,12 +3554,12 @@
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>PARTNER_DEPENDENCY</t>
+          <t>INDUSTRY_COMMENTARY</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
@@ -3564,7 +3568,7 @@
         </is>
       </c>
       <c r="M20" s="7" t="n">
-        <v>60</v>
+        <v>51.5</v>
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
@@ -3576,7 +3580,7 @@
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>Classified PARTNER_DEPENDENCY: vendor's own statement that its services integrate third-party AI models. Service relevance 0.00; no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
+          <t>Classified INDUSTRY_COMMENTARY: commentary/advocacy cue 'writing is on the wall'. Service relevance 0.50 (matched: core, banking); no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
         </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
@@ -3588,37 +3592,37 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>V-002</t>
+          <t>V-003</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Fiserv, Inc.</t>
+          <t>Financial Statement Services, Inc. (FSSI)</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>4d4019a96a74</t>
+          <t>c8367e0bd688</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>The team at Fiserv has seen an increasing number of AI use cases around client services and support, fraud prevention and even loan origination.</t>
+          <t>By leveraging artificial intelligence and machine learning, we can tap into the vast amount of customer data available to us.</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-4-technologies-shaping-the-future-of-financial-services.html</t>
+          <t>https://www.fssi-ca.com/use-predictive-analytics-to-forecast-your-consumers-next-purchase/</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>official_insights_article</t>
+          <t>official_product_page</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -3633,33 +3637,33 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2017-03-20</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>INDUSTRY_COMMENTARY</t>
+          <t>MARKETING_ONLY</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>Fraud Detection</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="M21" s="7" t="n">
-        <v>70.5</v>
+        <v>62.5</v>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>STRONG</t>
+          <t>MODERATE</t>
         </is>
       </c>
       <c r="O21" s="7" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>Classified INDUSTRY_COMMENTARY: commentary/advocacy cue 'has seen'. Service relevance 0.50 (matched: client servic, loan); no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
+          <t>Classified MARKETING_ONLY: capability or aspirational language 'can' without a concrete deployment statement. Service relevance 0.00; no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
@@ -3671,37 +3675,37 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>V-002</t>
+          <t>V-003</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Fiserv, Inc.</t>
+          <t>Financial Statement Services, Inc. (FSSI)</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>6ef5a6df4333</t>
+          <t>e3824d7e6a67</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>And White predicts the impact of AI on financial services will grow even larger as the industry addresses issues such as unintentional bias and privacy risk.</t>
+          <t>And the future of predictive analytics lies in the realm of artificial intelligence (AI).</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-4-technologies-shaping-the-future-of-financial-services.html</t>
+          <t>https://www.fssi-ca.com/use-predictive-analytics-to-forecast-your-consumers-next-purchase/</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>official_insights_article</t>
+          <t>official_product_page</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -3716,7 +3720,7 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2017-03-20</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -3726,11 +3730,11 @@
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Predictive Analytics</t>
         </is>
       </c>
       <c r="M22" s="7" t="n">
-        <v>60</v>
+        <v>46.5</v>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
@@ -3742,7 +3746,7 @@
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>Classified INDUSTRY_COMMENTARY: commentary/advocacy cue 'predicts'. Service relevance 0.00; no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
+          <t>Classified INDUSTRY_COMMENTARY: commentary/advocacy cue 'future of'. Service relevance 0.00; no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
@@ -3754,37 +3758,37 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>V-002</t>
+          <t>V-003</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Fiserv, Inc.</t>
+          <t>Financial Statement Services, Inc. (FSSI)</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>bf4b859dd63c</t>
+          <t>8db8c4d66ba3</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Although AI is likely the murkiest advancement reshaping core banking modernization, White believes “the writing is on the wall that this is where the industry is moving.”</t>
+          <t>AI has grown smarter with each passing day, thanks to machine learning capabilities.</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-4-technologies-shaping-the-future-of-financial-services.html</t>
+          <t>https://www.fssi-ca.com/use-predictive-analytics-to-forecast-your-consumers-next-purchase/</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>official_insights_article</t>
+          <t>official_product_page</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -3799,7 +3803,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2017-03-20</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
@@ -3809,11 +3813,11 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="M23" s="7" t="n">
-        <v>51.5</v>
+        <v>46.5</v>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
@@ -3825,7 +3829,7 @@
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>Classified INDUSTRY_COMMENTARY: commentary/advocacy cue 'writing is on the wall'. Service relevance 0.50 (matched: core, banking); no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
+          <t>Classified INDUSTRY_COMMENTARY: commentary/advocacy cue 'grown smarter'. Service relevance 0.00; no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
@@ -3847,7 +3851,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>a5365ca51d5c</t>
+          <t>f513baa4762d</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -3930,7 +3934,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>d354af5757d8</t>
+          <t>5c984246119f</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -4013,7 +4017,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>8f9706fb257d</t>
+          <t>f1bd6b10c72f</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -4096,27 +4100,27 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>b1b06f8ac290</t>
+          <t>d1456aa6e38b</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Digital employees handle everything from payment instruction validation to code security enhancements.</t>
+          <t>We have over 125 AI-enabled solutions in production ⁠–⁠ from predictive analytics and automation to anomaly detection ⁠–⁠ designed to help clients transform their business while optimizing our own infrastructure.</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>https://openai.com/index/bny/</t>
+          <t>https://www.bny.com/corporate/global/en/about-us/technology-innovation/artificial-intelligence.html</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>official_partner_announcement</t>
+          <t>official_ai_documentation</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -4131,7 +4135,7 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
@@ -4141,7 +4145,7 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>Agentic AI</t>
+          <t>Fraud Detection, Predictive Analytics, AI-assisted Automation</t>
         </is>
       </c>
       <c r="M27" s="7" t="n">
@@ -4157,7 +4161,7 @@
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>Classified PRODUCT_FEATURE: concrete deployment language 'handle' tied to products/clients. Service relevance 0.50 (matched: payment, validation); no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
+          <t>Classified PRODUCT_FEATURE: concrete deployment language 'in production' tied to products/clients. Service relevance 0.00; no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
@@ -4179,27 +4183,27 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>525f14b6b617</t>
+          <t>562ac6f4d7d2</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>We have over 125 AI-enabled solutions in production ⁠–⁠ from predictive analytics and automation to anomaly detection ⁠–⁠ designed to help clients transform their business while optimizing our own infrastructure.</t>
+          <t>Digital employees handle everything from payment instruction validation to code security enhancements.</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>https://www.bny.com/corporate/global/en/about-us/technology-innovation/artificial-intelligence.html</t>
+          <t>https://openai.com/index/bny/</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>official_ai_documentation</t>
+          <t>official_partner_announcement</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
@@ -4214,7 +4218,7 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
@@ -4224,7 +4228,7 @@
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
-          <t>Fraud Detection, Predictive Analytics, AI-assisted Automation</t>
+          <t>Agentic AI</t>
         </is>
       </c>
       <c r="M28" s="7" t="n">
@@ -4240,7 +4244,7 @@
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>Classified PRODUCT_FEATURE: concrete deployment language 'in production' tied to products/clients. Service relevance 0.00; no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
+          <t>Classified PRODUCT_FEATURE: concrete deployment language 'handle' tied to products/clients. Service relevance 0.50 (matched: payment, validation); no service-specific term — treated as vendor-level, not confirmed in the contracted service.</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
@@ -4262,7 +4266,7 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>4d6006ce272c</t>
+          <t>0624cae04080</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -4345,7 +4349,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>c1a7659eb110</t>
+          <t>37c22d320d9d</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -4428,7 +4432,7 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>4d28356ade26</t>
+          <t>03a4269b4ae4</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -4511,7 +4515,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>d8429140165f</t>
+          <t>1b2463ba0d3c</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -4594,7 +4598,7 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>303055c83102</t>
+          <t>94ff2aa90760</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -4677,7 +4681,7 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>5f104b9d74f3</t>
+          <t>ed5a65eb9ce4</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -4760,7 +4764,7 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>c315a5611cc2</t>
+          <t>686466e6a5a4</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -4843,7 +4847,7 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>dccf33baf070</t>
+          <t>34bdac37b262</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -4926,7 +4930,7 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>f38a87b2d5c3</t>
+          <t>a3cea840e976</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -5193,37 +5197,37 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>V-003</t>
+          <t>V-002</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Financial Statement Services, Inc. (FSSI)</t>
+          <t>Fiserv, Inc.</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>official_website</t>
+          <t>product_pages</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fssi-ca.com/</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-4-technologies-shaping-the-future-of-financial-services.html</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Print and Mail Outsourcing | Secure eDelivery | FSSI</t>
+          <t>Core Banking Modernization: 4 Technologies Shaping the Future of Financial Services | Fiserv</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>official_product_page</t>
+          <t>official_insights_article</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -5242,18 +5246,18 @@
         </is>
       </c>
       <c r="K4" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>V-003</t>
+          <t>V-002</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Financial Statement Services, Inc. (FSSI)</t>
+          <t>Fiserv, Inc.</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -5263,22 +5267,22 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://www.fssi-ca.com/use-predictive-analytics-to-forecast-your-consumers-next-purchase/</t>
+          <t>https://investors.fiserv.com/news-releases/news-release-details/fiserv-collaborates-microsoft-accelerate-ai-driven-innovation</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Understanding Customer Analytics: Predictive Insights for Success | FSSI</t>
+          <t>Fiserv Collaborates with Microsoft to Accelerate AI-Driven Innovation - Fiserv, Inc.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>official_product_page</t>
+          <t>official_press_release</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -5297,43 +5301,43 @@
         </is>
       </c>
       <c r="K5" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>V-002</t>
+          <t>V-003</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Fiserv, Inc.</t>
+          <t>Financial Statement Services, Inc. (FSSI)</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>product_pages</t>
+          <t>official_website</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-4-technologies-shaping-the-future-of-financial-services.html</t>
+          <t>https://www.fssi-ca.com/</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Core Banking Modernization: 4 Technologies Shaping the Future of Financial Services | Fiserv</t>
+          <t>Print and Mail Outsourcing | Secure eDelivery | FSSI</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>official_insights_article</t>
+          <t>official_product_page</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -5352,18 +5356,18 @@
         </is>
       </c>
       <c r="K6" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>V-002</t>
+          <t>V-003</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Fiserv, Inc.</t>
+          <t>Financial Statement Services, Inc. (FSSI)</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -5373,22 +5377,22 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://investors.fiserv.com/news-releases/news-release-details/fiserv-collaborates-microsoft-accelerate-ai-driven-innovation</t>
+          <t>https://www.fssi-ca.com/use-predictive-analytics-to-forecast-your-consumers-next-purchase/</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Fiserv Collaborates with Microsoft to Accelerate AI-Driven Innovation - Fiserv, Inc.</t>
+          <t>Understanding Customer Analytics: Predictive Insights for Success | FSSI</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>official_press_release</t>
+          <t>official_product_page</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -5407,7 +5411,7 @@
         </is>
       </c>
       <c r="K7" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -5806,7 +5810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5844,7 +5848,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>1.0.0+2ded6eb8</t>
+          <t>1.1.0+85b80c18</t>
         </is>
       </c>
     </row>
@@ -5885,16 +5889,18 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>criticality weight</t>
+          <t>Run</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>operational_dependency</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>0.3</v>
+          <t>Assessed by team</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Team MAVIRA</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -5905,11 +5911,11 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>data_sensitivity</t>
+          <t>operational_dependency</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
@@ -5920,11 +5926,11 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>payment_flow</t>
+          <t>data_sensitivity</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="8">
@@ -5935,7 +5941,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>regulatory_exposure</t>
+          <t>payment_flow</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
@@ -5950,7 +5956,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>data_volume</t>
+          <t>regulatory_exposure</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
@@ -5960,16 +5966,16 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>criticality threshold</t>
+          <t>criticality weight</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>data_volume</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>0.75</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="11">
@@ -5980,11 +5986,11 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="12">
@@ -5995,11 +6001,11 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>0.35</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="13">
@@ -6010,26 +6016,26 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>risk weight</t>
+          <t>criticality threshold</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>DATA_EXPOSURE</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -6040,11 +6046,11 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>AI_SUBPROCESSOR_RISK</t>
+          <t>DATA_EXPOSURE</t>
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="16">
@@ -6055,11 +6061,11 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>MODEL_PROVIDER_TRANSPARENCY</t>
+          <t>AI_SUBPROCESSOR_RISK</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="17">
@@ -6070,7 +6076,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>DATA_RETENTION_RISK</t>
+          <t>MODEL_PROVIDER_TRANSPARENCY</t>
         </is>
       </c>
       <c r="C17" s="7" t="n">
@@ -6085,7 +6091,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>MODEL_TRAINING_RISK</t>
+          <t>DATA_RETENTION_RISK</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
@@ -6100,11 +6106,11 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>DECISION_IMPACT</t>
+          <t>MODEL_TRAINING_RISK</t>
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="20">
@@ -6115,7 +6121,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>OPERATIONAL_DEPENDENCY</t>
+          <t>DECISION_IMPACT</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
@@ -6130,11 +6136,11 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>REGULATORY_RISK</t>
+          <t>OPERATIONAL_DEPENDENCY</t>
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="22">
@@ -6145,26 +6151,26 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CONTRACTUAL_RISK</t>
+          <t>REGULATORY_RISK</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>risk threshold</t>
+          <t>risk weight</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>CONTRACTUAL_RISK</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>75</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="24">
@@ -6175,11 +6181,11 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25">
@@ -6190,11 +6196,11 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
@@ -6205,26 +6211,26 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>0.01</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>evidence_strength weight</t>
+          <t>risk threshold</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>source_reliability</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>0.3</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="28">
@@ -6235,11 +6241,11 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>directness</t>
+          <t>source_reliability</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="29">
@@ -6250,7 +6256,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>specificity</t>
+          <t>directness</t>
         </is>
       </c>
       <c r="C29" s="7" t="n">
@@ -6265,11 +6271,11 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>service_relevance</t>
+          <t>specificity</t>
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="31">
@@ -6280,11 +6286,11 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>independence</t>
+          <t>service_relevance</t>
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="32">
@@ -6295,26 +6301,26 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>recency</t>
+          <t>independence</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>evidence_strength threshold</t>
+          <t>evidence_strength weight</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>VERY_STRONG</t>
+          <t>recency</t>
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>80</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="34">
@@ -6325,11 +6331,11 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>STRONG</t>
+          <t>VERY_STRONG</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35">
@@ -6340,11 +6346,11 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>MODERATE</t>
+          <t>STRONG</t>
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36">
@@ -6355,28 +6361,26 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>WEAK</t>
+          <t>MODERATE</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>assessment depth</t>
+          <t>evidence_strength threshold</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>LOW — Baseline review</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Limited business impact. Confirm whether AI is part of the service from the vendor's own product material; deeper work is not proportionate.</t>
-        </is>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -6387,12 +6391,12 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>MEDIUM — Standard review</t>
+          <t>LOW — Baseline review</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Moderate impact. Adds hiring, engineering and trust material, which reveal AI that marketing pages omit.</t>
+          <t>Limited business impact. Confirm whether AI is part of the service from the vendor's own product material; deeper work is not proportionate.</t>
         </is>
       </c>
     </row>
@@ -6404,12 +6408,12 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>HIGH — Enhanced review</t>
+          <t>MEDIUM — Standard review</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>High impact. Adds regulatory/investor disclosures, sub-processor lists and executive statements, where model providers and AI risk factors are disclosed.</t>
+          <t>Moderate impact. Adds hiring, engineering and trust material, which reveal AI that marketing pages omit.</t>
         </is>
       </c>
     </row>
@@ -6421,29 +6425,182 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>CRITICAL — Full review</t>
+          <t>HIGH — Enhanced review</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Critical impact. Everything in Enhanced plus targeted provider and sub-processor searches, corroboration across independent sources, a recorded negative-evidence review, and mandatory analyst sign-off.</t>
+          <t>High impact. Adds regulatory/investor disclosures, sub-processor lists and executive statements, where model providers and AI risk factors are disclosed.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
+          <t>assessment depth</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>CRITICAL — Full review</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Critical impact. Everything in Enhanced plus targeted provider and sub-processor searches, corroboration across independent sources, a recorded negative-evidence review, and mandatory analyst sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Collection methods</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>LIVE = fetched during the run; CACHED = verbatim snapshot captured in an earlier analyst session (retrieval date shown); DEMO_MOCK = fictional test data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>regulatory standard</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>NIST AI RMF (2023)</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>AI risk identification (MAP-1.1), sub-processor disclosure (GV-6.2), data-flow mapping (MS-2.5), retention (MS-2.6), ongoing monitoring (MS-2.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>regulatory standard</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>FFIEC SR 11-7 / OCC 2011-12</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Model Risk Management — third-party AI models are in scope where vendor output influences Meridian decisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>regulatory standard</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>OCC 2023-17</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Third-party AI arrangements; sub-processor disclosure (§III.C); AI contract clauses (§IV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>regulatory standard</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>OCC 2026-46</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Prohibition on training on client data without consent; AI governance expectations for supervised institutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>regulatory standard</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Fed SR 23-4</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Federal Reserve guidance on AI in banking and model risk oversight</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>regulatory standard</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>CFPB Circular 2022-03</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Explainability requirements for AI-driven credit and payment decisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>regulatory standard</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>NIST CSF 2.0 / SP 800-161r1</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>AI supply-chain risk governance (GV.SC-07); Cyber Supply-Chain Risk Management (C-SCRM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>regulatory standard</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>OWASP LLM 2026 / Agentic Top-10</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Prompt injection (LLM01); third-party model supply-chain (LLM09); agentic scope restriction; immutable audit logs</t>
         </is>
       </c>
     </row>
